--- a/satisfaction_surveys/017_policyholder_satisfaction_assessment_form--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/017_policyholder_satisfaction_assessment_form--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -800,8 +800,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'text':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'text': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'text':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'text': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'text':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'text': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'text':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'text': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'text':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'text': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'text':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'text': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
